--- a/tests/abiotic/profile.xlsx
+++ b/tests/abiotic/profile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{43711640-811F-4CCA-97B5-0666522CA4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64ABC18D-964C-48D4-80C0-D8E7FDC770D2}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{43711640-811F-4CCA-97B5-0666522CA4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB140C7E-A67F-4C22-8E13-58D25E41BF40}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D7BD78CA-9E1A-A84E-ABC8-B9A18946ED57}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D7BD78CA-9E1A-A84E-ABC8-B9A18946ED57}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,11 +82,9 @@
   </si>
   <si>
     <t>CO2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>N2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -97,14 +95,14 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -154,6 +152,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -474,15 +476,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7F68D6-EB94-CE47-9BFF-C3E1342F35B3}">
   <dimension ref="A1:P101"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="12.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.08203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.4140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="11.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -532,7 +534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -549,7 +551,7 @@
         <v>293.0541661580404</v>
       </c>
       <c r="F2">
-        <v>2.2108556616427028E+19</v>
+        <v>2.2311863544377123E+19</v>
       </c>
       <c r="G2">
         <v>2.2564587148341056E+17</v>
@@ -558,13 +560,13 @@
         <v>225645871483.41055</v>
       </c>
       <c r="I2">
-        <v>225645871483410.56</v>
+        <v>2256458714.8341055</v>
       </c>
       <c r="J2">
         <v>99999.999999999985</v>
       </c>
       <c r="K2">
-        <v>2.2564587148341056E+17</v>
+        <v>2.2564587148341056E+16</v>
       </c>
       <c r="L2">
         <v>34999.999999999993</v>
@@ -580,10 +582,10 @@
       </c>
       <c r="P2" s="1">
         <f>SUM(F2:O2)</f>
-        <v>2.2564587148341064E+19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+        <v>2.256458714834106E+19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -600,7 +602,7 @@
         <v>286.10833231608075</v>
       </c>
       <c r="F3">
-        <v>1.9469959359592157E+19</v>
+        <v>1.9649002148019634E+19</v>
       </c>
       <c r="G3">
         <v>1.9871563863999386E+17</v>
@@ -609,13 +611,13 @@
         <v>198715638639.99387</v>
       </c>
       <c r="I3">
-        <v>198715638639993.88</v>
+        <v>1987156386.3999386</v>
       </c>
       <c r="J3">
         <v>88065.266753441741</v>
       </c>
       <c r="K3">
-        <v>1.9871563863999386E+17</v>
+        <v>1.9871563863999388E+16</v>
       </c>
       <c r="L3">
         <v>30822.843363704607</v>
@@ -634,7 +636,7 @@
         <v>1.987156386399939E+19</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -651,7 +653,7 @@
         <v>279.16249847412109</v>
       </c>
       <c r="F4">
-        <v>1.7041247038477156E+19</v>
+        <v>1.7197955757365533E+19</v>
       </c>
       <c r="G4">
         <v>1.7392754786642899E+17</v>
@@ -660,13 +662,13 @@
         <v>173927547866.42899</v>
       </c>
       <c r="I4">
-        <v>173927547866429</v>
+        <v>1739275478.66429</v>
       </c>
       <c r="J4">
         <v>77079.87153632284</v>
       </c>
       <c r="K4">
-        <v>1.7392754786642899E+17</v>
+        <v>1.73927547866429E+16</v>
       </c>
       <c r="L4">
         <v>26977.955037712989</v>
@@ -682,10 +684,10 @@
       </c>
       <c r="P4" s="1">
         <f t="shared" si="0"/>
-        <v>1.7392754786642899E+19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.7392754786642897E+19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -702,7 +704,7 @@
         <v>272.21666463216144</v>
       </c>
       <c r="F5">
-        <v>1.481741404153352E+19</v>
+        <v>1.4953672730022955E+19</v>
       </c>
       <c r="G5">
         <v>1.5123051054577158E+17</v>
@@ -711,13 +713,13 @@
         <v>151230510545.77158</v>
       </c>
       <c r="I5">
-        <v>151230510545771.59</v>
+        <v>1512305105.457716</v>
       </c>
       <c r="J5">
         <v>67021.173288734426</v>
       </c>
       <c r="K5">
-        <v>1.5123051054577158E+17</v>
+        <v>1.5123051054577158E+16</v>
       </c>
       <c r="L5">
         <v>23457.410651057049</v>
@@ -736,7 +738,7 @@
         <v>1.512305105457716E+19</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -753,7 +755,7 @@
         <v>265.27083079020184</v>
       </c>
       <c r="F6">
-        <v>1.2792673816375742E+19</v>
+        <v>1.2910313301349738E+19</v>
       </c>
       <c r="G6">
         <v>1.3056546756898229E+17</v>
@@ -762,13 +764,13 @@
         <v>130565467568.98228</v>
       </c>
       <c r="I6">
-        <v>130565467568982.3</v>
+        <v>1305654675.6898229</v>
       </c>
       <c r="J6">
         <v>57862.998649448557</v>
       </c>
       <c r="K6">
-        <v>1.3056546756898229E+17</v>
+        <v>1.3056546756898228E+16</v>
       </c>
       <c r="L6">
         <v>20252.049527306994</v>
@@ -787,7 +789,7 @@
         <v>1.3056546756898228E+19</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -804,7 +806,7 @@
         <v>258.32499694824219</v>
       </c>
       <c r="F7">
-        <v>1.0960461286543059E+19</v>
+        <v>1.1061252023439348E+19</v>
       </c>
       <c r="G7">
         <v>1.118654140010468E+17</v>
@@ -813,13 +815,13 @@
         <v>111865414001.0468</v>
       </c>
       <c r="I7">
-        <v>111865414001046.8</v>
+        <v>1118654140.010468</v>
       </c>
       <c r="J7">
         <v>49575.652887259275</v>
       </c>
       <c r="K7">
-        <v>1.118654140010468E+17</v>
+        <v>1.118654140010468E+16</v>
       </c>
       <c r="L7">
         <v>17351.478510540746</v>
@@ -838,7 +840,7 @@
         <v>1.1186541400104679E+19</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -855,7 +857,7 @@
         <v>251.37916310628256</v>
       </c>
       <c r="F8">
-        <v>9.3134417476327731E+18</v>
+        <v>9.3990867430616678E+18</v>
       </c>
       <c r="G8">
         <v>9.5055489877303712E+16</v>
@@ -864,13 +866,13 @@
         <v>95055489877.303711</v>
       </c>
       <c r="I8">
-        <v>95055489877303.719</v>
+        <v>950554898.77303708</v>
       </c>
       <c r="J8">
         <v>42125.960139400187</v>
       </c>
       <c r="K8">
-        <v>9.5055489877303712E+16</v>
+        <v>9505548987730370</v>
       </c>
       <c r="L8">
         <v>14744.086048790065</v>
@@ -886,10 +888,10 @@
       </c>
       <c r="P8" s="1">
         <f t="shared" si="0"/>
-        <v>9.5055489877303706E+18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+        <v>9.5055489877303685E+18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -906,7 +908,7 @@
         <v>244.43332926432291</v>
       </c>
       <c r="F9">
-        <v>7.8435346730345318E+18</v>
+        <v>7.9156626263112212E+18</v>
       </c>
       <c r="G9">
         <v>8.0053223171167504E+16</v>
@@ -915,13 +917,13 @@
         <v>80053223171.167496</v>
       </c>
       <c r="I9">
-        <v>80053223171167.5</v>
+        <v>800532231.71167505</v>
       </c>
       <c r="J9">
         <v>35477.371088109183</v>
       </c>
       <c r="K9">
-        <v>8.0053223171167504E+16</v>
+        <v>8005322317116750</v>
       </c>
       <c r="L9">
         <v>12417.079880838211</v>
@@ -940,7 +942,7 @@
         <v>8.0053223171167488E+18</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -957,7 +959,7 @@
         <v>237.48749542236328</v>
       </c>
       <c r="F10">
-        <v>6.5419490578693243E+18</v>
+        <v>6.6021078275636419E+18</v>
       </c>
       <c r="G10">
         <v>6.6768890523870104E+16</v>
@@ -966,13 +968,13 @@
         <v>66768890523.87011</v>
       </c>
       <c r="I10">
-        <v>66768890523870.109</v>
+        <v>667688905.23870111</v>
       </c>
       <c r="J10">
         <v>29590.12282605797</v>
       </c>
       <c r="K10">
-        <v>6.6768890523870104E+16</v>
+        <v>6676889052387011</v>
       </c>
       <c r="L10">
         <v>10356.542989120289</v>
@@ -991,7 +993,7 @@
         <v>6.6768890523870106E+18</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1008,7 +1010,7 @@
         <v>230.54166158040366</v>
       </c>
       <c r="F11">
-        <v>5.3992310678787891E+18</v>
+        <v>5.4488815765369405E+18</v>
       </c>
       <c r="G11">
         <v>5.5106003561833024E+16</v>
@@ -1017,13 +1019,13 @@
         <v>55106003561.833023</v>
       </c>
       <c r="I11">
-        <v>55106003561833.023</v>
+        <v>551060035.61833024</v>
       </c>
       <c r="J11">
         <v>24421.454378740716</v>
       </c>
       <c r="K11">
-        <v>5.5106003561833024E+16</v>
+        <v>5510600356183302</v>
       </c>
       <c r="L11">
         <v>8547.50903255925</v>
@@ -1042,7 +1044,7 @@
         <v>5.5106003561833032E+18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1059,7 +1061,7 @@
         <v>223.595827738444</v>
       </c>
       <c r="F12">
-        <v>4.4053305894589373E+18</v>
+        <v>4.4458413403092214E+18</v>
       </c>
       <c r="G12">
         <v>4.4961988124199696E+16</v>
@@ -1068,13 +1070,13 @@
         <v>44961988124.199699</v>
       </c>
       <c r="I12">
-        <v>44961988124199.695</v>
+        <v>449619881.24199694</v>
       </c>
       <c r="J12">
         <v>19925.907719302228</v>
       </c>
       <c r="K12">
-        <v>4.4961988124199696E+16</v>
+        <v>4496198812419969.5</v>
       </c>
       <c r="L12">
         <v>6974.06770175578</v>
@@ -1093,7 +1095,7 @@
         <v>4.49619881241997E+18</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1110,7 +1112,7 @@
         <v>216.64999389648438</v>
       </c>
       <c r="F13">
-        <v>3.7586350770307773E+18</v>
+        <v>3.7931989141936614E+18</v>
       </c>
       <c r="G13">
         <v>3.836163989622724E+16</v>
@@ -1119,13 +1121,13 @@
         <v>38361639896.227234</v>
       </c>
       <c r="I13">
-        <v>38361639896227.242</v>
+        <v>383616398.96227235</v>
       </c>
       <c r="J13">
         <v>17000.816209946734</v>
       </c>
       <c r="K13">
-        <v>3.836163989622724E+16</v>
+        <v>3836163989622723.5</v>
       </c>
       <c r="L13">
         <v>5950.2856734813558</v>
@@ -1144,7 +1146,7 @@
         <v>3.8361639896227236E+18</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1161,7 +1163,7 @@
         <v>216.64999389648438</v>
       </c>
       <c r="F14">
-        <v>3.2100400269259228E+18</v>
+        <v>3.239559067349676E+18</v>
       </c>
       <c r="G14">
         <v>3.2762531355581104E+16</v>
@@ -1170,13 +1172,13 @@
         <v>32762531355.581104</v>
       </c>
       <c r="I14">
-        <v>32762531355581.105</v>
+        <v>327625313.55581105</v>
       </c>
       <c r="J14">
         <v>14519.446396336923</v>
       </c>
       <c r="K14">
-        <v>3.2762531355581104E+16</v>
+        <v>3276253135558110.5</v>
       </c>
       <c r="L14">
         <v>5081.8062387179225</v>
@@ -1195,7 +1197,7 @@
         <v>3.2762531355581097E+18</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1212,7 +1214,7 @@
         <v>216.64999389648438</v>
       </c>
       <c r="F15">
-        <v>2.7415156734520637E+18</v>
+        <v>2.7667262350986998E+18</v>
       </c>
       <c r="G15">
         <v>2.7980645867305568E+16</v>
@@ -1221,13 +1223,13 @@
         <v>27980645867.305569</v>
       </c>
       <c r="I15">
-        <v>27980645867305.57</v>
+        <v>279806458.67305571</v>
       </c>
       <c r="J15">
         <v>12400.247202999546</v>
       </c>
       <c r="K15">
-        <v>2.7980645867305568E+16</v>
+        <v>2798064586730557</v>
       </c>
       <c r="L15">
         <v>4340.0865210498405</v>
@@ -1246,7 +1248,7 @@
         <v>2.7980645867305569E+18</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1263,7 +1265,7 @@
         <v>216.64999389648438</v>
       </c>
       <c r="F16">
-        <v>2.3413752242151603E+18</v>
+        <v>2.3629061550792745E+18</v>
       </c>
       <c r="G16">
         <v>2.3896704886882744E+16</v>
@@ -1272,13 +1274,13 @@
         <v>23896704886.882744</v>
       </c>
       <c r="I16">
-        <v>23896704886882.746</v>
+        <v>238967048.86882746</v>
       </c>
       <c r="J16">
         <v>10590.357682941087</v>
       </c>
       <c r="K16">
-        <v>2.3896704886882744E+16</v>
+        <v>2389670488688274.5</v>
       </c>
       <c r="L16">
         <v>3706.6251890293806</v>
@@ -1297,7 +1299,7 @@
         <v>2.3896704886882749E+18</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1314,7 +1316,7 @@
         <v>216.64999389648438</v>
       </c>
       <c r="F17">
-        <v>1.9996376433864105E+18</v>
+        <v>2.0180260073734195E+18</v>
       </c>
       <c r="G17">
         <v>2.0408839279797368E+16</v>
@@ -1323,13 +1325,13 @@
         <v>20408839279.797367</v>
       </c>
       <c r="I17">
-        <v>20408839279797.371</v>
+        <v>204088392.79797369</v>
       </c>
       <c r="J17">
         <v>9044.6322574520582</v>
       </c>
       <c r="K17">
-        <v>2.0408839279797368E+16</v>
+        <v>2040883927979736.8</v>
       </c>
       <c r="L17">
         <v>3165.6212901082204</v>
@@ -1348,7 +1350,7 @@
         <v>2.0408839279797363E+18</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1365,7 +1367,7 @@
         <v>216.64999389648438</v>
       </c>
       <c r="F18">
-        <v>1.7077786864291643E+18</v>
+        <v>1.7234831597867139E+18</v>
       </c>
       <c r="G18">
         <v>1.743004831503921E+16</v>
@@ -1374,13 +1376,13 @@
         <v>17430048315.039207</v>
       </c>
       <c r="I18">
-        <v>17430048315039.211</v>
+        <v>174300483.15039209</v>
       </c>
       <c r="J18">
         <v>7724.514612411449</v>
       </c>
       <c r="K18">
-        <v>1.743004831503921E+16</v>
+        <v>1743004831503921</v>
       </c>
       <c r="L18">
         <v>2703.5801143440071</v>
@@ -1396,10 +1398,10 @@
       </c>
       <c r="P18" s="1">
         <f t="shared" si="0"/>
-        <v>1.7430048315039209E+18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.7430048315039204E+18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1416,7 +1418,7 @@
         <v>216.64999389648438</v>
       </c>
       <c r="F19">
-        <v>1.458518272781953E+18</v>
+        <v>1.4719305852428242E+18</v>
       </c>
       <c r="G19">
         <v>1.4886029533553056E+16</v>
@@ -1425,13 +1427,13 @@
         <v>14886029533.553055</v>
       </c>
       <c r="I19">
-        <v>14886029533553.057</v>
+        <v>148860295.33553055</v>
       </c>
       <c r="J19">
         <v>6597.0759560949782</v>
       </c>
       <c r="K19">
-        <v>1.4886029533553056E+16</v>
+        <v>1488602953355305.5</v>
       </c>
       <c r="L19">
         <v>2308.9765846332425</v>
@@ -1447,10 +1449,10 @@
       </c>
       <c r="P19" s="1">
         <f t="shared" si="0"/>
-        <v>1.4886029533553055E+18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.4886029533553057E+18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1467,7 +1469,7 @@
         <v>216.64999389648438</v>
       </c>
       <c r="F20">
-        <v>1.245638892757717E+18</v>
+        <v>1.257093598780161E+18</v>
       </c>
       <c r="G20">
         <v>1.2713325360240998E+16</v>
@@ -1476,13 +1478,13 @@
         <v>12713325360.240999</v>
       </c>
       <c r="I20">
-        <v>12713325360241</v>
+        <v>127133253.60240999</v>
       </c>
       <c r="J20">
         <v>5634.1936489521277</v>
       </c>
       <c r="K20">
-        <v>1.2713325360240998E+16</v>
+        <v>1271332536024099.8</v>
       </c>
       <c r="L20">
         <v>1971.9677771332445</v>
@@ -1498,10 +1500,10 @@
       </c>
       <c r="P20" s="1">
         <f t="shared" si="0"/>
-        <v>1.2713325360240996E+18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.2713325360240998E+18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1518,7 +1520,7 @@
         <v>216.64999389648438</v>
       </c>
       <c r="F21">
-        <v>1.0638305190315812E+18</v>
+        <v>1.0736133428692604E+18</v>
       </c>
       <c r="G21">
         <v>1.0857740228919772E+16</v>
@@ -1527,13 +1529,13 @@
         <v>10857740228.919771</v>
       </c>
       <c r="I21">
-        <v>10857740228919.771</v>
+        <v>108577402.28919771</v>
       </c>
       <c r="J21">
         <v>4811.8497172318212</v>
       </c>
       <c r="K21">
-        <v>1.0857740228919772E+16</v>
+        <v>1085774022891977.1</v>
       </c>
       <c r="L21">
         <v>1684.1474010311374</v>
@@ -1552,7 +1554,7 @@
         <v>1.0857740228919772E+18</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1569,7 +1571,7 @@
         <v>217.58097839355469</v>
       </c>
       <c r="F22">
-        <v>9.215301509171296E+17</v>
+        <v>9.300044021876599E+17</v>
       </c>
       <c r="G22">
         <v>9405384422401960</v>
@@ -1578,13 +1580,13 @@
         <v>9405384422.4019604</v>
       </c>
       <c r="I22">
-        <v>9405384422401.9609</v>
+        <v>94053844.224019602</v>
       </c>
       <c r="J22">
         <v>4168.2058530786999</v>
       </c>
       <c r="K22">
-        <v>9405384422401960</v>
+        <v>940538442240196</v>
       </c>
       <c r="L22">
         <v>1458.8720485775448</v>
@@ -1600,10 +1602,10 @@
       </c>
       <c r="P22" s="1">
         <f t="shared" si="0"/>
-        <v>9.4053844224019584E+17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+        <v>9.4053844224019597E+17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1620,7 +1622,7 @@
         <v>218.57426452636719</v>
       </c>
       <c r="F23">
-        <v>8.0002593833958605E+17</v>
+        <v>8.07382855329968E+17</v>
       </c>
       <c r="G23">
         <v>8165279769183932</v>
@@ -1629,13 +1631,13 @@
         <v>8165279769.1839323</v>
       </c>
       <c r="I23">
-        <v>8165279769183.9326</v>
+        <v>81652797.691839322</v>
       </c>
       <c r="J23">
         <v>3618.6258208514314</v>
       </c>
       <c r="K23">
-        <v>8165279769183932</v>
+        <v>816527976918393.25</v>
       </c>
       <c r="L23">
         <v>1266.519037298001</v>
@@ -1654,7 +1656,7 @@
         <v>8.1652797691839309E+17</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1671,7 +1673,7 @@
         <v>219.56723022460938</v>
       </c>
       <c r="F24">
-        <v>6.9542755216704051E+17</v>
+        <v>7.0182259828858982E+17</v>
       </c>
       <c r="G24">
         <v>7097720524446737</v>
@@ -1680,13 +1682,13 @@
         <v>7097720524.4467363</v>
       </c>
       <c r="I24">
-        <v>7097720524446.7373</v>
+        <v>70977205.244467363</v>
       </c>
       <c r="J24">
         <v>3145.513134269137</v>
       </c>
       <c r="K24">
-        <v>7097720524446737</v>
+        <v>709772052444673.63</v>
       </c>
       <c r="L24">
         <v>1100.9295969941979</v>
@@ -1705,7 +1707,7 @@
         <v>7.0977205244467379E+17</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1722,7 +1724,7 @@
         <v>220.55989074707031</v>
       </c>
       <c r="F25">
-        <v>6.052647728381513E+17</v>
+        <v>6.1083069573836928E+17</v>
       </c>
       <c r="G25">
         <v>6177494963366143</v>
@@ -1731,13 +1733,13 @@
         <v>6177494963.3661432</v>
       </c>
       <c r="I25">
-        <v>6177494963366.1436</v>
+        <v>61774949.633661427</v>
       </c>
       <c r="J25">
         <v>2737.6946552378249</v>
       </c>
       <c r="K25">
-        <v>6177494963366143</v>
+        <v>617749496336614.25</v>
       </c>
       <c r="L25">
         <v>958.19312933323874</v>
@@ -1753,10 +1755,10 @@
       </c>
       <c r="P25" s="1">
         <f t="shared" si="0"/>
-        <v>6.1774949633661414E+17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
+        <v>6.1774949633661427E+17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1773,7 +1775,7 @@
         <v>221.55224609375</v>
       </c>
       <c r="F26">
-        <v>5.2744478099318214E+17</v>
+        <v>5.3229508307067546E+17</v>
       </c>
       <c r="G26">
         <v>5383243209018563</v>
@@ -1782,13 +1784,13 @@
         <v>5383243209.0185623</v>
       </c>
       <c r="I26">
-        <v>5383243209018.5635</v>
+        <v>53832432.090185627</v>
       </c>
       <c r="J26">
         <v>2385.7042779594294</v>
       </c>
       <c r="K26">
-        <v>5383243209018563</v>
+        <v>538324320901856.25</v>
       </c>
       <c r="L26">
         <v>834.99649728580027</v>
@@ -1804,10 +1806,10 @@
       </c>
       <c r="P26" s="1">
         <f t="shared" si="0"/>
-        <v>5.3832432090185619E+17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+        <v>5.3832432090185626E+17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1824,7 +1826,7 @@
         <v>222.54428100585938</v>
       </c>
       <c r="F27">
-        <v>4.6019207306211968E+17</v>
+        <v>4.6442392945439667E+17</v>
       </c>
       <c r="G27">
         <v>4696843994723027</v>
@@ -1833,13 +1835,13 @@
         <v>4696843994.7230272</v>
       </c>
       <c r="I27">
-        <v>4696843994723.0273</v>
+        <v>46968439.947230272</v>
       </c>
       <c r="J27">
         <v>2081.5111589880507</v>
       </c>
       <c r="K27">
-        <v>4696843994723027</v>
+        <v>469684399472302.75</v>
       </c>
       <c r="L27">
         <v>728.52890564581776</v>
@@ -1858,7 +1860,7 @@
         <v>4.6968439947230266E+17</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1875,7 +1877,7 @@
         <v>223.5360107421875</v>
       </c>
       <c r="F28">
-        <v>4.0199865951605792E+17</v>
+        <v>4.0569537811801043E+17</v>
       </c>
       <c r="G28">
         <v>4102906374008386</v>
@@ -1884,13 +1886,13 @@
         <v>4102906374.0083861</v>
       </c>
       <c r="I28">
-        <v>4102906374008.3862</v>
+        <v>41029063.740083858</v>
       </c>
       <c r="J28">
         <v>1818.294457166716</v>
       </c>
       <c r="K28">
-        <v>4102906374008386</v>
+        <v>410290637400838.63</v>
       </c>
       <c r="L28">
         <v>636.40306000835062</v>
@@ -1909,7 +1911,7 @@
         <v>4.1029063740083859E+17</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1926,7 +1928,7 @@
         <v>224.52743530273438</v>
       </c>
       <c r="F29">
-        <v>3.515816818814873E+17</v>
+        <v>3.5481477361637434E+17</v>
       </c>
       <c r="G29">
         <v>3588337148468829</v>
@@ -1935,13 +1937,13 @@
         <v>3588337148.4688287</v>
       </c>
       <c r="I29">
-        <v>3588337148468.8291</v>
+        <v>35883371.484688289</v>
       </c>
       <c r="J29">
         <v>1590.2516296349088</v>
       </c>
       <c r="K29">
-        <v>3588337148468829</v>
+        <v>358833714846882.88</v>
       </c>
       <c r="L29">
         <v>556.58807037221811</v>
@@ -1957,10 +1959,10 @@
       </c>
       <c r="P29" s="1">
         <f t="shared" si="0"/>
-        <v>3.5883371484688288E+17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
+        <v>3.5883371484688294E+17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1977,7 +1979,7 @@
         <v>225.5185546875</v>
       </c>
       <c r="F30">
-        <v>3.0784846552835546E+17</v>
+        <v>3.1067939324953542E+17</v>
       </c>
       <c r="G30">
         <v>3141984187125222.5</v>
@@ -1986,13 +1988,13 @@
         <v>3141984187.1252227</v>
       </c>
       <c r="I30">
-        <v>3141984187125.2227</v>
+        <v>31419841.871252224</v>
       </c>
       <c r="J30">
         <v>1392.4403608493321</v>
       </c>
       <c r="K30">
-        <v>3141984187125222.5</v>
+        <v>314198418712522.25</v>
       </c>
       <c r="L30">
         <v>487.35412629726619</v>
@@ -2008,10 +2010,10 @@
       </c>
       <c r="P30" s="1">
         <f t="shared" si="0"/>
-        <v>3.1419841871252243E+17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+        <v>3.1419841871252237E+17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2028,7 +2030,7 @@
         <v>226.50933837890625</v>
       </c>
       <c r="F31">
-        <v>2.698669403226279E+17</v>
+        <v>2.7234859570810515E+17</v>
       </c>
       <c r="G31">
         <v>2754334531654382</v>
@@ -2037,13 +2039,13 @@
         <v>2754334531.6543818</v>
       </c>
       <c r="I31">
-        <v>2754334531654.3818</v>
+        <v>27543345.316543818</v>
       </c>
       <c r="J31">
         <v>1220.6447711838059</v>
       </c>
       <c r="K31">
-        <v>2754334531654382</v>
+        <v>275433453165438.19</v>
       </c>
       <c r="L31">
         <v>427.22566991433206</v>
@@ -2059,10 +2061,10 @@
       </c>
       <c r="P31" s="1">
         <f t="shared" si="0"/>
-        <v>2.7543345316543811E+17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+        <v>2.7543345316543814E+17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2079,7 +2081,7 @@
         <v>227.49983215332031</v>
       </c>
       <c r="F32">
-        <v>2.3684155902958646E+17</v>
+        <v>2.3901951802585302E+17</v>
       </c>
       <c r="G32">
         <v>2417268613140132.5</v>
@@ -2088,13 +2090,13 @@
         <v>2417268613.1401324</v>
       </c>
       <c r="I32">
-        <v>2417268613140.1328</v>
+        <v>24172686.131401327</v>
       </c>
       <c r="J32">
         <v>1071.2664926013722</v>
       </c>
       <c r="K32">
-        <v>2417268613140132.5</v>
+        <v>241726861314013.25</v>
       </c>
       <c r="L32">
         <v>374.94327241048029</v>
@@ -2110,10 +2112,10 @@
       </c>
       <c r="P32" s="1">
         <f t="shared" si="0"/>
-        <v>2.4172686131401325E+17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
+        <v>2.4172686131401322E+17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2130,7 +2132,7 @@
         <v>228.49002075195313</v>
       </c>
       <c r="F33">
-        <v>2.0809175468136096E+17</v>
+        <v>2.1000533484446294E+17</v>
       </c>
       <c r="G33">
         <v>2123840382175803.5</v>
@@ -2139,13 +2141,13 @@
         <v>2123840382.1758037</v>
       </c>
       <c r="I33">
-        <v>2123840382175.8037</v>
+        <v>21238403.821758036</v>
       </c>
       <c r="J33">
         <v>941.22722840597055</v>
       </c>
       <c r="K33">
-        <v>2123840382175803.5</v>
+        <v>212384038217580.34</v>
       </c>
       <c r="L33">
         <v>329.42952994208969</v>
@@ -2161,10 +2163,10 @@
       </c>
       <c r="P33" s="1">
         <f t="shared" si="0"/>
-        <v>2.1238403821758035E+17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
+        <v>2.1238403821758032E+17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2181,7 +2183,7 @@
         <v>230.97369384765625</v>
       </c>
       <c r="F34">
-        <v>1.8894704288635488E+17</v>
+        <v>1.9068457118822227E+17</v>
       </c>
       <c r="G34">
         <v>1928444307604698.5</v>
@@ -2190,13 +2192,13 @@
         <v>1928444307.6046987</v>
       </c>
       <c r="I34">
-        <v>1928444307604.6987</v>
+        <v>19284443.076046985</v>
       </c>
       <c r="J34">
         <v>854.63310049813049</v>
       </c>
       <c r="K34">
-        <v>1928444307604698.5</v>
+        <v>192844430760469.88</v>
       </c>
       <c r="L34">
         <v>299.12158517434563</v>
@@ -2215,7 +2217,7 @@
         <v>1.9284443076046989E+17</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2232,7 +2234,7 @@
         <v>233.74447631835938</v>
       </c>
       <c r="F35">
-        <v>1.7297075958495606E+17</v>
+        <v>1.7456137241267376E+17</v>
       </c>
       <c r="G35">
         <v>1765386065895177.3</v>
@@ -2241,13 +2243,13 @@
         <v>1765386065.8951774</v>
       </c>
       <c r="I35">
-        <v>1765386065895.1775</v>
+        <v>17653860.658951774</v>
       </c>
       <c r="J35">
         <v>782.37020437795513</v>
       </c>
       <c r="K35">
-        <v>1765386065895177.3</v>
+        <v>176538606589517.72</v>
       </c>
       <c r="L35">
         <v>273.82957153228426</v>
@@ -2266,7 +2268,7 @@
         <v>1.765386065895177E+17</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2283,7 +2285,7 @@
         <v>236.51438903808594</v>
       </c>
       <c r="F36">
-        <v>1.5867048814390746E+17</v>
+        <v>1.6012959784792637E+17</v>
       </c>
       <c r="G36">
         <v>1619433651734988.5</v>
@@ -2292,13 +2294,13 @@
         <v>1619433651.7349885</v>
       </c>
       <c r="I36">
-        <v>1619433651734.9885</v>
+        <v>16194336.517349886</v>
       </c>
       <c r="J36">
         <v>717.68813720753087</v>
       </c>
       <c r="K36">
-        <v>1619433651734988.5</v>
+        <v>161943365173498.84</v>
       </c>
       <c r="L36">
         <v>251.19084802263581</v>
@@ -2314,10 +2316,10 @@
       </c>
       <c r="P36" s="1">
         <f t="shared" si="0"/>
-        <v>1.6194336517349882E+17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.6194336517349885E+17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2334,7 +2336,7 @@
         <v>239.28343200683594</v>
       </c>
       <c r="F37">
-        <v>1.4584083716616576E+17</v>
+        <v>1.4718196734885222E+17</v>
       </c>
       <c r="G37">
         <v>1488490785317851.3</v>
@@ -2343,13 +2345,13 @@
         <v>1488490785.3178513</v>
       </c>
       <c r="I37">
-        <v>1488490785317.8513</v>
+        <v>14884907.853178512</v>
       </c>
       <c r="J37">
         <v>659.65788584227857</v>
       </c>
       <c r="K37">
-        <v>1488490785317851.3</v>
+        <v>148849078531785.13</v>
       </c>
       <c r="L37">
         <v>230.8802600447975</v>
@@ -2365,10 +2367,10 @@
       </c>
       <c r="P37" s="1">
         <f t="shared" si="0"/>
-        <v>1.4884907853178515E+17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.4884907853178512E+17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2385,7 +2387,7 @@
         <v>242.05162048339844</v>
       </c>
       <c r="F38">
-        <v>1.3430491757646808E+17</v>
+        <v>1.355399651951251E+17</v>
       </c>
       <c r="G38">
         <v>1370752089194840.5</v>
@@ -2394,13 +2396,13 @@
         <v>1370752089.1948404</v>
       </c>
       <c r="I38">
-        <v>1370752089194.8406</v>
+        <v>13707520.891948406</v>
       </c>
       <c r="J38">
         <v>607.47935700459641</v>
       </c>
       <c r="K38">
-        <v>1370752089194840.5</v>
+        <v>137075208919484.05</v>
       </c>
       <c r="L38">
         <v>212.61777495160874</v>
@@ -2416,10 +2418,10 @@
       </c>
       <c r="P38" s="1">
         <f t="shared" si="0"/>
-        <v>1.3707520891948408E+17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.3707520891948406E+17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2436,7 +2438,7 @@
         <v>244.81892395019531</v>
       </c>
       <c r="F39">
-        <v>1.2390979742735557E+17</v>
+        <v>1.2504925310033045E+17</v>
       </c>
       <c r="G39">
         <v>1264656698802940.3</v>
@@ -2445,13 +2447,13 @@
         <v>1264656698.8029404</v>
       </c>
       <c r="I39">
-        <v>1264656698802.9404</v>
+        <v>12646566.988029404</v>
       </c>
       <c r="J39">
         <v>560.46081875507195</v>
       </c>
       <c r="K39">
-        <v>1264656698802940.3</v>
+        <v>126465669880294.03</v>
       </c>
       <c r="L39">
         <v>196.16128656427517</v>
@@ -2467,10 +2469,10 @@
       </c>
       <c r="P39" s="1">
         <f t="shared" si="0"/>
-        <v>1.2646566988029405E+17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.2646566988029403E+17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2487,7 +2489,7 @@
         <v>247.58538818359375</v>
       </c>
       <c r="F40">
-        <v>1.1452321861274352E+17</v>
+        <v>1.1557635673293242E+17</v>
       </c>
       <c r="G40">
         <v>1168854752361212.3</v>
@@ -2496,13 +2498,13 @@
         <v>1168854752.3612123</v>
       </c>
       <c r="I40">
-        <v>1168854752361.2124</v>
+        <v>11688547.523612123</v>
       </c>
       <c r="J40">
         <v>518.00404974267224</v>
       </c>
       <c r="K40">
-        <v>1168854752361212.3</v>
+        <v>116885475236121.23</v>
       </c>
       <c r="L40">
         <v>181.30141740993525</v>
@@ -2518,10 +2520,10 @@
       </c>
       <c r="P40" s="1">
         <f t="shared" si="0"/>
-        <v>1.1688547523612123E+17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.1688547523612122E+17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2538,7 +2540,7 @@
         <v>250.35098266601563</v>
       </c>
       <c r="F41">
-        <v>1.0603013431262707E+17</v>
+        <v>1.0700517131984712E+17</v>
       </c>
       <c r="G41">
         <v>1082172051100746.1</v>
@@ -2547,13 +2549,13 @@
         <v>1082172051.1007462</v>
       </c>
       <c r="I41">
-        <v>1082172051100.7462</v>
+        <v>10821720.511007462</v>
       </c>
       <c r="J41">
         <v>479.58867759754565</v>
       </c>
       <c r="K41">
-        <v>1082172051100746.1</v>
+        <v>108217205110074.61</v>
       </c>
       <c r="L41">
         <v>167.85603715914095</v>
@@ -2572,7 +2574,7 @@
         <v>1.0821720511007461E+17</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2589,7 +2591,7 @@
         <v>253.11570739746094</v>
       </c>
       <c r="F42">
-        <v>9.8330463695786496E+16</v>
+        <v>9.9234695701735024E+16</v>
       </c>
       <c r="G42">
         <v>1003587143156946.4</v>
@@ -2598,13 +2600,13 @@
         <v>1003587143.1569464</v>
       </c>
       <c r="I42">
-        <v>1003587143156.9465</v>
+        <v>10035871.431569465</v>
       </c>
       <c r="J42">
         <v>444.76202314684491</v>
       </c>
       <c r="K42">
-        <v>1003587143156946.4</v>
+        <v>100358714315694.64</v>
       </c>
       <c r="L42">
         <v>155.6667081013957</v>
@@ -2623,7 +2625,7 @@
         <v>1.0035871431569462E+17</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2640,7 +2642,7 @@
         <v>255.87957763671875</v>
       </c>
       <c r="F43">
-        <v>9.13368958125712E+16</v>
+        <v>9.2176816030716704E+16</v>
       </c>
       <c r="G43">
         <v>932208909508985.25</v>
@@ -2649,13 +2651,13 @@
         <v>932208909.50898528</v>
       </c>
       <c r="I43">
-        <v>932208909508.98535</v>
+        <v>9322089.0950898528</v>
       </c>
       <c r="J43">
         <v>413.12916712394673</v>
       </c>
       <c r="K43">
-        <v>932208909508985.25</v>
+        <v>93220890950898.531</v>
       </c>
       <c r="L43">
         <v>144.59520849338134</v>
@@ -2674,7 +2676,7 @@
         <v>9.3220890950898528E+16</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2691,7 +2693,7 @@
         <v>258.642578125</v>
       </c>
       <c r="F44">
-        <v>8.4972991595050736E+16</v>
+        <v>8.5754390316805504E+16</v>
       </c>
       <c r="G44">
         <v>867257192483171.25</v>
@@ -2700,13 +2702,13 @@
         <v>867257192.48317122</v>
       </c>
       <c r="I44">
-        <v>867257192483.17126</v>
+        <v>8672571.9248317126</v>
       </c>
       <c r="J44">
         <v>384.34436525772276</v>
       </c>
       <c r="K44">
-        <v>867257192483171.25</v>
+        <v>86725719248317.125</v>
       </c>
       <c r="L44">
         <v>134.52052784020296</v>
@@ -2722,10 +2724,10 @@
       </c>
       <c r="P44" s="1">
         <f t="shared" si="0"/>
-        <v>8.672571924831712E+16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
+        <v>8.6725719248317136E+16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2742,7 +2744,7 @@
         <v>261.40469360351563</v>
       </c>
       <c r="F45">
-        <v>7.9171734499446688E+16</v>
+        <v>7.9899785742267456E+16</v>
       </c>
       <c r="G45">
         <v>808048003220030.25</v>
@@ -2751,13 +2753,13 @@
         <v>808048003.22003031</v>
       </c>
       <c r="I45">
-        <v>808048003220.03027</v>
+        <v>8080480.0322003029</v>
       </c>
       <c r="J45">
         <v>358.10449263169335</v>
       </c>
       <c r="K45">
-        <v>808048003220030.25</v>
+        <v>80804800322003.031</v>
       </c>
       <c r="L45">
         <v>125.33657242109267</v>
@@ -2776,7 +2778,7 @@
         <v>8.0804800322003024E+16</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2793,7 +2795,7 @@
         <v>264.16598510742188</v>
       </c>
       <c r="F46">
-        <v>7.3874362020700272E+16</v>
+        <v>7.4553699430974352E+16</v>
       </c>
       <c r="G46">
         <v>753981595797900.38</v>
@@ -2802,13 +2804,13 @@
         <v>753981595.79790032</v>
       </c>
       <c r="I46">
-        <v>753981595797.90039</v>
+        <v>7539815.9579790039</v>
       </c>
       <c r="J46">
         <v>334.14375846594334</v>
       </c>
       <c r="K46">
-        <v>753981595797900.38</v>
+        <v>75398159579790.031</v>
       </c>
       <c r="L46">
         <v>116.95031546308016</v>
@@ -2824,10 +2826,10 @@
       </c>
       <c r="P46" s="1">
         <f t="shared" si="0"/>
-        <v>7.5398159579790032E+16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
+        <v>7.5398159579790016E+16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2844,7 +2846,7 @@
         <v>266.9263916015625</v>
       </c>
       <c r="F47">
-        <v>6.9028925007669776E+16</v>
+        <v>6.966370451528264E+16</v>
       </c>
       <c r="G47">
         <v>704527763216588.38</v>
@@ -2853,13 +2855,13 @@
         <v>704527763.21658838</v>
       </c>
       <c r="I47">
-        <v>704527763216.58838</v>
+        <v>7045277.6321658837</v>
       </c>
       <c r="J47">
         <v>312.22718970437046</v>
       </c>
       <c r="K47">
-        <v>704527763216588.38</v>
+        <v>70452776321658.828</v>
       </c>
       <c r="L47">
         <v>109.27951639652966</v>
@@ -2875,10 +2877,10 @@
       </c>
       <c r="P47" s="1">
         <f t="shared" si="0"/>
-        <v>7.0452776321658832E+16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
+        <v>7.0452776321658824E+16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2895,7 +2897,7 @@
         <v>269.68597412109375</v>
       </c>
       <c r="F48">
-        <v>6.4589765544051312E+16</v>
+        <v>6.5183723215626344E+16</v>
       </c>
       <c r="G48">
         <v>659220508509704.63</v>
@@ -2904,13 +2906,13 @@
         <v>659220508.50970471</v>
       </c>
       <c r="I48">
-        <v>659220508509.70471</v>
+        <v>6592205.0850970466</v>
       </c>
       <c r="J48">
         <v>292.14826939927877</v>
       </c>
       <c r="K48">
-        <v>659220508509704.63</v>
+        <v>65922050850970.469</v>
       </c>
       <c r="L48">
         <v>102.25189428974755</v>
@@ -2926,10 +2928,10 @@
       </c>
       <c r="P48" s="1">
         <f t="shared" si="0"/>
-        <v>6.5922050850970472E+16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
+        <v>6.5922050850970464E+16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2946,7 +2948,7 @@
         <v>270.64999389648438</v>
       </c>
       <c r="F49">
-        <v>5.8147352613582024E+16</v>
+        <v>5.8682066834568952E+16</v>
       </c>
       <c r="G49">
         <v>593467510456832.75</v>
@@ -2955,13 +2957,13 @@
         <v>593467510.45683277</v>
       </c>
       <c r="I49">
-        <v>593467510456.83276</v>
+        <v>5934675.1045683278</v>
       </c>
       <c r="J49">
         <v>263.00836197681741</v>
       </c>
       <c r="K49">
-        <v>593467510456832.75</v>
+        <v>59346751045683.273</v>
       </c>
       <c r="L49">
         <v>92.0529266918861</v>
@@ -2977,10 +2979,10 @@
       </c>
       <c r="P49" s="1">
         <f t="shared" si="0"/>
-        <v>5.934675104568328E+16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
+        <v>5.9346751045683272E+16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2997,7 +2999,7 @@
         <v>270.64999389648438</v>
       </c>
       <c r="F50">
-        <v>5.1248512379435248E+16</v>
+        <v>5.1719785913689112E+16</v>
       </c>
       <c r="G50">
         <v>523056092657526.25</v>
@@ -3006,13 +3008,13 @@
         <v>523056092.65752625</v>
       </c>
       <c r="I50">
-        <v>523056092657.52631</v>
+        <v>5230560.926575263</v>
       </c>
       <c r="J50">
         <v>231.80397195788322</v>
       </c>
       <c r="K50">
-        <v>523056092657526.25</v>
+        <v>52305609265752.625</v>
       </c>
       <c r="L50">
         <v>81.131390185259121</v>
@@ -3028,10 +3030,10 @@
       </c>
       <c r="P50" s="1">
         <f t="shared" si="0"/>
-        <v>5.2305609265752632E+16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
+        <v>5.2305609265752624E+16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3048,7 +3050,7 @@
         <v>270.64999389648438</v>
       </c>
       <c r="F51">
-        <v>4.5168178825937688E+16</v>
+        <v>4.5583538536547592E+16</v>
       </c>
       <c r="G51">
         <v>460998574050935.75</v>
@@ -3057,13 +3059,13 @@
         <v>460998574.05093575</v>
       </c>
       <c r="I51">
-        <v>460998574050.93579</v>
+        <v>4609985.7405093573</v>
       </c>
       <c r="J51">
         <v>204.30179866367652</v>
       </c>
       <c r="K51">
-        <v>460998574050935.75</v>
+        <v>46099857405093.578</v>
       </c>
       <c r="L51">
         <v>71.505629532286775</v>
@@ -3082,7 +3084,7 @@
         <v>4.6099857405093576E+16</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3099,7 +3101,7 @@
         <v>270.64999389648438</v>
       </c>
       <c r="F52">
-        <v>3.9809240965803192E+16</v>
+        <v>4.0175320697972088E+16</v>
       </c>
       <c r="G52">
         <v>406303813797929.5</v>
@@ -3108,13 +3110,13 @@
         <v>406303813.79792953</v>
       </c>
       <c r="I52">
-        <v>406303813797.92957</v>
+        <v>4063038.1379792956</v>
       </c>
       <c r="J52">
         <v>180.06259592824009</v>
       </c>
       <c r="K52">
-        <v>406303813797929.5</v>
+        <v>40630381379792.953</v>
       </c>
       <c r="L52">
         <v>63.02190857488403</v>
@@ -3133,7 +3135,7 @@
         <v>4.063038137979296E+16</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3150,7 +3152,7 @@
         <v>269.02914428710938</v>
       </c>
       <c r="F53">
-        <v>3.3724976986440924E+16</v>
+        <v>3.4035106751366708E+16</v>
       </c>
       <c r="G53">
         <v>344206180208487.38</v>
@@ -3159,13 +3161,13 @@
         <v>344206180.20848739</v>
       </c>
       <c r="I53">
-        <v>344206180208.48737</v>
+        <v>3442061.8020848739</v>
       </c>
       <c r="J53">
         <v>152.54264478479203</v>
       </c>
       <c r="K53">
-        <v>344206180208487.38</v>
+        <v>34420618020848.738</v>
       </c>
       <c r="L53">
         <v>53.389925674677215</v>
@@ -3181,10 +3183,10 @@
       </c>
       <c r="P53" s="1">
         <f t="shared" si="0"/>
-        <v>3.4420618020848732E+16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.4">
+        <v>3.4420618020848728E+16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3201,7 +3203,7 @@
         <v>266.27471923828125</v>
       </c>
       <c r="F54">
-        <v>2.7702609885737512E+16</v>
+        <v>2.7957358877713064E+16</v>
       </c>
       <c r="G54">
         <v>282740282800171.75</v>
@@ -3210,13 +3212,13 @@
         <v>282740282.80017173</v>
       </c>
       <c r="I54">
-        <v>282740282800.17175</v>
+        <v>2827402.8280017171</v>
       </c>
       <c r="J54">
         <v>125.30266161814474</v>
       </c>
       <c r="K54">
-        <v>282740282800171.75</v>
+        <v>28274028280017.172</v>
       </c>
       <c r="L54">
         <v>43.855931566350655</v>
@@ -3235,7 +3237,7 @@
         <v>2.8274028280017172E+16</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3252,7 +3254,7 @@
         <v>263.52117919921875</v>
       </c>
       <c r="F55">
-        <v>2.2662822930769756E+16</v>
+        <v>2.2871226807543344E+16</v>
       </c>
       <c r="G55">
         <v>231302862471272.5</v>
@@ -3261,13 +3263,13 @@
         <v>231302862.4712725</v>
       </c>
       <c r="I55">
-        <v>231302862471.27249</v>
+        <v>2313028.6247127247</v>
       </c>
       <c r="J55">
         <v>102.50702171091032</v>
       </c>
       <c r="K55">
-        <v>231302862471272.5</v>
+        <v>23130286247127.25</v>
       </c>
       <c r="L55">
         <v>35.877457598818609</v>
@@ -3286,7 +3288,7 @@
         <v>2.3130286247127248E+16</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3303,7 +3305,7 @@
         <v>260.76849365234375</v>
       </c>
       <c r="F56">
-        <v>1.8461878594846524E+16</v>
+        <v>1.8631651225707328E+16</v>
       </c>
       <c r="G56">
         <v>188426895388538.09</v>
@@ -3312,13 +3314,13 @@
         <v>188426895.38853809</v>
       </c>
       <c r="I56">
-        <v>188426895388.53809</v>
+        <v>1884268.9538853809</v>
       </c>
       <c r="J56">
         <v>83.505580735781905</v>
       </c>
       <c r="K56">
-        <v>188426895388538.09</v>
+        <v>18842689538853.809</v>
       </c>
       <c r="L56">
         <v>29.226953257523665</v>
@@ -3334,10 +3336,10 @@
       </c>
       <c r="P56" s="1">
         <f t="shared" si="0"/>
-        <v>1.8842689538853812E+16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.8842689538853808E+16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3354,7 +3356,7 @@
         <v>258.01666259765625</v>
       </c>
       <c r="F57">
-        <v>1.4974371715738654E+16</v>
+        <v>1.5112073763155336E+16</v>
       </c>
       <c r="G57">
         <v>152832462758052.66</v>
@@ -3363,13 +3365,13 @@
         <v>152832462.75805268</v>
       </c>
       <c r="I57">
-        <v>152832462758.05267</v>
+        <v>1528324.6275805268</v>
       </c>
       <c r="J57">
         <v>67.731114136200304</v>
       </c>
       <c r="K57">
-        <v>152832462758052.66</v>
+        <v>15283246275805.266</v>
       </c>
       <c r="L57">
         <v>23.705889947670105</v>
@@ -3385,10 +3387,10 @@
       </c>
       <c r="P57" s="1">
         <f t="shared" si="0"/>
-        <v>1.5283246275805264E+16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.5283246275805266E+16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3405,7 +3407,7 @@
         <v>255.26568603515625</v>
       </c>
       <c r="F58">
-        <v>1.209127164572173E+16</v>
+        <v>1.2202461142890226E+16</v>
       </c>
       <c r="G58">
         <v>123406768482313.55</v>
@@ -3414,13 +3416,13 @@
         <v>123406768.48231354</v>
       </c>
       <c r="I58">
-        <v>123406768482.31355</v>
+        <v>1234067.6848231354</v>
       </c>
       <c r="J58">
         <v>54.690461505468484</v>
       </c>
       <c r="K58">
-        <v>123406768482313.55</v>
+        <v>12340676848231.354</v>
       </c>
       <c r="L58">
         <v>19.141661526913968</v>
@@ -3439,7 +3441,7 @@
         <v>1.2340676848231354E+16</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3456,7 +3458,7 @@
         <v>252.51556396484375</v>
       </c>
       <c r="F59">
-        <v>9718141743564390</v>
+        <v>9807508298674532</v>
       </c>
       <c r="G59">
         <v>99185966816873.375</v>
@@ -3465,13 +3467,13 @@
         <v>99185966.816873387</v>
       </c>
       <c r="I59">
-        <v>99185966816.873383</v>
+        <v>991859.66816873383</v>
       </c>
       <c r="J59">
         <v>43.956473107537228</v>
       </c>
       <c r="K59">
-        <v>99185966816873.375</v>
+        <v>9918596681687.3379</v>
       </c>
       <c r="L59">
         <v>15.384765587638029</v>
@@ -3490,7 +3492,7 @@
         <v>9918596681687340</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3507,7 +3509,7 @@
         <v>249.76629638671875</v>
       </c>
       <c r="F60">
-        <v>7773504803385136</v>
+        <v>7844988772619349</v>
       </c>
       <c r="G60">
         <v>79338479497889.141</v>
@@ -3516,13 +3518,13 @@
         <v>79338479.497889146</v>
       </c>
       <c r="I60">
-        <v>79338479497.889145</v>
+        <v>793384.79497889138</v>
       </c>
       <c r="J60">
         <v>35.160616490039388</v>
       </c>
       <c r="K60">
-        <v>79338479497889.141</v>
+        <v>7933847949788.9141</v>
       </c>
       <c r="L60">
         <v>12.306215771513784</v>
@@ -3541,7 +3543,7 @@
         <v>7933847949788913</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3558,7 +3560,7 @@
         <v>247.01789855957028</v>
       </c>
       <c r="F61">
-        <v>6187351136886287</v>
+        <v>6244249077969161</v>
       </c>
       <c r="G61">
         <v>63149768828382.68</v>
@@ -3567,13 +3569,13 @@
         <v>63149768.828382678</v>
       </c>
       <c r="I61">
-        <v>63149768828.382683</v>
+        <v>631497.68828382681</v>
       </c>
       <c r="J61">
         <v>27.986228337896019</v>
       </c>
       <c r="K61">
-        <v>63149768828382.68</v>
+        <v>6314976882838.2686</v>
       </c>
       <c r="L61">
         <v>9.7951799182636066</v>
@@ -3589,10 +3591,10 @@
       </c>
       <c r="P61" s="1">
         <f t="shared" si="0"/>
-        <v>6314976882838269</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.4">
+        <v>6314976882838268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3609,7 +3611,7 @@
         <v>244.27033996582031</v>
       </c>
       <c r="F62">
-        <v>4899762982282964</v>
+        <v>4944820458304324</v>
       </c>
       <c r="G62">
         <v>50008298026018.867</v>
@@ -3618,13 +3620,13 @@
         <v>50008298.026018873</v>
       </c>
       <c r="I62">
-        <v>50008298026.018875</v>
+        <v>500082.98026018869</v>
       </c>
       <c r="J62">
         <v>22.162292488340725</v>
       </c>
       <c r="K62">
-        <v>50008298026018.867</v>
+        <v>5000829802601.8867</v>
       </c>
       <c r="L62">
         <v>7.756802370919254</v>
@@ -3643,7 +3645,7 @@
         <v>5000829802601887</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3660,7 +3662,7 @@
         <v>241.52363586425781</v>
       </c>
       <c r="F63">
-        <v>3859698792710158.5</v>
+        <v>3895191996449001.5</v>
       </c>
       <c r="G63">
         <v>39393123343811.57</v>
@@ -3669,13 +3671,13 @@
         <v>39393123.343811572</v>
       </c>
       <c r="I63">
-        <v>39393123343.811577</v>
+        <v>393931.23343811574</v>
       </c>
       <c r="J63">
         <v>17.457941102506606</v>
       </c>
       <c r="K63">
-        <v>39393123343811.57</v>
+        <v>3939312334381.1572</v>
       </c>
       <c r="L63">
         <v>6.1102793858773126</v>
@@ -3691,10 +3693,10 @@
       </c>
       <c r="P63" s="1">
         <f t="shared" si="0"/>
-        <v>3939312334381157</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.4">
+        <v>3939312334381156.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3711,7 +3713,7 @@
         <v>238.77778625488281</v>
       </c>
       <c r="F64">
-        <v>3023860878594858.5</v>
+        <v>3051667843854581</v>
       </c>
       <c r="G64">
         <v>30862336923802.25</v>
@@ -3720,13 +3722,13 @@
         <v>30862336.923802249</v>
       </c>
       <c r="I64">
-        <v>30862336923.802254</v>
+        <v>308623.36923802254</v>
       </c>
       <c r="J64">
         <v>13.677332858301925</v>
       </c>
       <c r="K64">
-        <v>30862336923802.25</v>
+        <v>3086233692380.2251</v>
       </c>
       <c r="L64">
         <v>4.7870665004056736</v>
@@ -3742,10 +3744,10 @@
       </c>
       <c r="P64" s="1">
         <f t="shared" si="0"/>
-        <v>3086233692380225.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
+        <v>3086233692380224.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3762,7 +3764,7 @@
         <v>236.03280639648438</v>
       </c>
       <c r="F65">
-        <v>2355694397937243.5</v>
+        <v>2377357005747561</v>
       </c>
       <c r="G65">
         <v>24042850222804</v>
@@ -3771,13 +3773,13 @@
         <v>24042850.222803999</v>
       </c>
       <c r="I65">
-        <v>24042850222.804001</v>
+        <v>240428.50222804002</v>
       </c>
       <c r="J65">
         <v>10.655125247692212</v>
       </c>
       <c r="K65">
-        <v>24042850222804</v>
+        <v>2404285022280.3999</v>
       </c>
       <c r="L65">
         <v>3.7292938366922739</v>
@@ -3793,10 +3795,10 @@
       </c>
       <c r="P65" s="1">
         <f t="shared" si="0"/>
-        <v>2404285022280399.5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
+        <v>2404285022280399</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3813,7 +3815,7 @@
         <v>233.2886657714844</v>
       </c>
       <c r="F66">
-        <v>1824479495301366.5</v>
+        <v>1841257131568315.5</v>
       </c>
       <c r="G66">
         <v>18621128138912.52</v>
@@ -3822,13 +3824,13 @@
         <v>18621128.138912521</v>
       </c>
       <c r="I66">
-        <v>18621128138.912521</v>
+        <v>186211.28138912522</v>
       </c>
       <c r="J66">
         <v>8.2523681982284973</v>
       </c>
       <c r="K66">
-        <v>18621128138912.52</v>
+        <v>1862112813891.252</v>
       </c>
       <c r="L66">
         <v>2.8883288693799738</v>
@@ -3847,7 +3849,7 @@
         <v>1862112813891252.3</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3864,7 +3866,7 @@
         <v>230.54537963867188</v>
       </c>
       <c r="F67">
-        <v>1404535810244919</v>
+        <v>1417451708181223.8</v>
       </c>
       <c r="G67">
         <v>14335070010716.588</v>
@@ -3873,13 +3875,13 @@
         <v>14335070.010716587</v>
       </c>
       <c r="I67">
-        <v>14335070010.716589</v>
+        <v>143350.70010716587</v>
       </c>
       <c r="J67">
         <v>6.3529059567883559</v>
       </c>
       <c r="K67">
-        <v>14335070010716.588</v>
+        <v>1433507001071.6587</v>
       </c>
       <c r="L67">
         <v>2.2235170848759243</v>
@@ -3898,7 +3900,7 @@
         <v>1433507001071658.5</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3915,7 +3917,7 @@
         <v>227.80293273925781</v>
       </c>
       <c r="F68">
-        <v>1074500314302536.5</v>
+        <v>1084381255956590.3</v>
       </c>
       <c r="G68">
         <v>10966639027436.332</v>
@@ -3924,13 +3926,13 @@
         <v>10966639.027436333</v>
       </c>
       <c r="I68">
-        <v>10966639027.436333</v>
+        <v>109666.39027436332</v>
       </c>
       <c r="J68">
         <v>4.8601106483096439</v>
       </c>
       <c r="K68">
-        <v>10966639027436.332</v>
+        <v>1096663902743.6333</v>
       </c>
       <c r="L68">
         <v>1.7010387269083755</v>
@@ -3949,7 +3951,7 @@
         <v>1096663902743633.3</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3966,7 +3968,7 @@
         <v>225.06135559082031</v>
       </c>
       <c r="F69">
-        <v>816700180260116.13</v>
+        <v>824210431046076.5</v>
       </c>
       <c r="G69">
         <v>8335461564167.6729</v>
@@ -3975,13 +3977,13 @@
         <v>8335461.5641676728</v>
       </c>
       <c r="I69">
-        <v>8335461564.1676731</v>
+        <v>83354.615641676734</v>
       </c>
       <c r="J69">
         <v>3.6940456784650251</v>
       </c>
       <c r="K69">
-        <v>8335461564167.6729</v>
+        <v>833546156416.76721</v>
       </c>
       <c r="L69">
         <v>1.2929159874627587</v>
@@ -4000,7 +4002,7 @@
         <v>833546156416767.25</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4017,7 +4019,7 @@
         <v>222.32064819335938</v>
       </c>
       <c r="F70">
-        <v>616592575184550</v>
+        <v>622262666834244.88</v>
       </c>
       <c r="G70">
         <v>6293109558963.2949</v>
@@ -4026,13 +4028,13 @@
         <v>6293109.5589632951</v>
       </c>
       <c r="I70">
-        <v>6293109558.9632959</v>
+        <v>62931.095589632954</v>
       </c>
       <c r="J70">
         <v>2.7889318415586271</v>
       </c>
       <c r="K70">
-        <v>6293109558963.2949</v>
+        <v>629310955896.32947</v>
       </c>
       <c r="L70">
         <v>0.97612614454551938</v>
@@ -4048,10 +4050,10 @@
       </c>
       <c r="P70" s="1">
         <f t="shared" si="1"/>
-        <v>629310955896329.38</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
+        <v>629310955896329.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4068,7 +4070,7 @@
         <v>219.58074951171875</v>
       </c>
       <c r="F71">
-        <v>462279084148625.06</v>
+        <v>466530132377798.38</v>
       </c>
       <c r="G71">
         <v>4718144590848.7891</v>
@@ -4077,13 +4079,13 @@
         <v>4718144.5908487886</v>
       </c>
       <c r="I71">
-        <v>4718144590.8487892</v>
+        <v>47181.445908487891</v>
       </c>
       <c r="J71">
         <v>2.0909509931785593</v>
       </c>
       <c r="K71">
-        <v>4718144590848.7891</v>
+        <v>471814459084.87891</v>
       </c>
       <c r="L71">
         <v>0.73183284761249567</v>
@@ -4099,10 +4101,10 @@
       </c>
       <c r="P71" s="1">
         <f t="shared" si="1"/>
-        <v>471814459084878.94</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
+        <v>471814459084878.88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4119,7 +4121,7 @@
         <v>216.84172058105469</v>
       </c>
       <c r="F72">
-        <v>344087134713519.56</v>
+        <v>347251307731208.88</v>
       </c>
       <c r="G72">
         <v>3511845785580.2588</v>
@@ -4128,13 +4130,13 @@
         <v>3511845.7855802588</v>
       </c>
       <c r="I72">
-        <v>3511845785.5802588</v>
+        <v>35118.45785580259</v>
       </c>
       <c r="J72">
         <v>1.5563527763628722</v>
       </c>
       <c r="K72">
-        <v>3511845785580.2588</v>
+        <v>351184578558.02588</v>
       </c>
       <c r="L72">
         <v>0.54472347172700519</v>
@@ -4150,10 +4152,10 @@
       </c>
       <c r="P72" s="1">
         <f t="shared" si="1"/>
-        <v>351184578558025.94</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
+        <v>351184578558025.88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4170,7 +4172,7 @@
         <v>214.25968933105469</v>
       </c>
       <c r="F73">
-        <v>256335947909242.56</v>
+        <v>258693174344091.81</v>
       </c>
       <c r="G73">
         <v>2616233586028.417</v>
@@ -4179,13 +4181,13 @@
         <v>2616233.5860284171</v>
       </c>
       <c r="I73">
-        <v>2616233586.0284171</v>
+        <v>26162.335860284169</v>
       </c>
       <c r="J73">
         <v>1.1594422573872625</v>
       </c>
       <c r="K73">
-        <v>2616233586028.417</v>
+        <v>261623358602.84171</v>
       </c>
       <c r="L73">
         <v>0.40580479008554188</v>
@@ -4204,7 +4206,7 @@
         <v>261623358602841.66</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4221,7 +4223,7 @@
         <v>212.304443359375</v>
       </c>
       <c r="F74">
-        <v>196311366399410.41</v>
+        <v>198116615901528.28</v>
       </c>
       <c r="G74">
         <v>2003606572867.8455</v>
@@ -4230,13 +4232,13 @@
         <v>2003606.5728678454</v>
       </c>
       <c r="I74">
-        <v>2003606572.8678455</v>
+        <v>20036.065728678455</v>
       </c>
       <c r="J74">
         <v>0.88794293451770512</v>
       </c>
       <c r="K74">
-        <v>2003606572867.8455</v>
+        <v>200360657286.78455</v>
       </c>
       <c r="L74">
         <v>0.31078002708119679</v>
@@ -4255,7 +4257,7 @@
         <v>200360657286784.5</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4272,7 +4274,7 @@
         <v>210.34982299804688</v>
       </c>
       <c r="F75">
-        <v>149603908762478.06</v>
+        <v>150979643579884.72</v>
       </c>
       <c r="G75">
         <v>1526897705522.3772</v>
@@ -4281,13 +4283,13 @@
         <v>1526897.7055223773</v>
       </c>
       <c r="I75">
-        <v>1526897705.5223773</v>
+        <v>15268.977055223773</v>
       </c>
       <c r="J75">
         <v>0.67667876903062874</v>
       </c>
       <c r="K75">
-        <v>1526897705522.3772</v>
+        <v>152689770552.23773</v>
       </c>
       <c r="L75">
         <v>0.23683756916072005</v>
@@ -4303,10 +4305,10 @@
       </c>
       <c r="P75" s="1">
         <f t="shared" si="1"/>
-        <v>152689770552237.78</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
+        <v>152689770552237.75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4323,7 +4325,7 @@
         <v>208.39579772949219</v>
       </c>
       <c r="F76">
-        <v>113433702541276.95</v>
+        <v>114476821637190.08</v>
       </c>
       <c r="G76">
         <v>1157734858480.0085</v>
@@ -4332,13 +4334,13 @@
         <v>1157734.8584800086</v>
       </c>
       <c r="I76">
-        <v>1157734858.4800086</v>
+        <v>11577.348584800086</v>
       </c>
       <c r="J76">
         <v>0.51307602078823089</v>
       </c>
       <c r="K76">
-        <v>1157734858480.0085</v>
+        <v>115773485848.00084</v>
       </c>
       <c r="L76">
         <v>0.17957660727588082</v>
@@ -4354,10 +4356,10 @@
       </c>
       <c r="P76" s="1">
         <f t="shared" si="1"/>
-        <v>115773485848000.86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.4">
+        <v>115773485848000.83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4374,7 +4376,7 @@
         <v>206.44239807128909</v>
       </c>
       <c r="F77">
-        <v>85562284571783.172</v>
+        <v>86349102342227.578</v>
       </c>
       <c r="G77">
         <v>873271675002.35315</v>
@@ -4383,13 +4385,13 @@
         <v>873271.67500235315</v>
       </c>
       <c r="I77">
-        <v>873271675.00235319</v>
+        <v>8732.7167500235319</v>
       </c>
       <c r="J77">
         <v>0.38700981731303508</v>
       </c>
       <c r="K77">
-        <v>873271675002.35315</v>
+        <v>87327167500.235321</v>
       </c>
       <c r="L77">
         <v>0.13545343605956225</v>
@@ -4408,7 +4410,7 @@
         <v>87327167500235.328</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4425,7 +4427,7 @@
         <v>204.48957824707031</v>
       </c>
       <c r="F78">
-        <v>64194655212390.07</v>
+        <v>64784979509379.641</v>
       </c>
       <c r="G78">
         <v>655187906261.32654</v>
@@ -4434,13 +4436,13 @@
         <v>655187.90626132651</v>
       </c>
       <c r="I78">
-        <v>655187906.26132655</v>
+        <v>6551.879062613265</v>
       </c>
       <c r="J78">
         <v>0.29036113178321354</v>
       </c>
       <c r="K78">
-        <v>655187906261.32654</v>
+        <v>65518790626.132652</v>
       </c>
       <c r="L78">
         <v>0.10162639612412475</v>
@@ -4459,7 +4461,7 @@
         <v>65518790626132.648</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4476,7 +4478,7 @@
         <v>202.53738403320315</v>
       </c>
       <c r="F79">
-        <v>47899033666187.07</v>
+        <v>48339505903041.055</v>
       </c>
       <c r="G79">
         <v>488870412589.0025</v>
@@ -4485,13 +4487,13 @@
         <v>488870.41258900252</v>
       </c>
       <c r="I79">
-        <v>488870412.58900255</v>
+        <v>4888.7041258900254</v>
       </c>
       <c r="J79">
         <v>0.21665382547224851</v>
       </c>
       <c r="K79">
-        <v>488870412589.0025</v>
+        <v>48887041258.900253</v>
       </c>
       <c r="L79">
         <v>7.5828838915286967E-2</v>
@@ -4510,7 +4512,7 @@
         <v>48887041258900.25</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4527,7 +4529,7 @@
         <v>200.58578491210938</v>
       </c>
       <c r="F80">
-        <v>35538293913880.516</v>
+        <v>35865098665794.984</v>
       </c>
       <c r="G80">
         <v>362713380179.36688</v>
@@ -4536,13 +4538,13 @@
         <v>362713.38017936685</v>
       </c>
       <c r="I80">
-        <v>362713380.17936689</v>
+        <v>3627.1338017936687</v>
       </c>
       <c r="J80">
         <v>0.16074452317468324</v>
       </c>
       <c r="K80">
-        <v>362713380179.36688</v>
+        <v>36271338017.936691</v>
       </c>
       <c r="L80">
         <v>5.6260583111139129E-2</v>
@@ -4558,10 +4560,10 @@
       </c>
       <c r="P80" s="1">
         <f t="shared" si="1"/>
-        <v>36271338017936.695</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.4">
+        <v>36271338017936.688</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4578,7 +4580,7 @@
         <v>198.63479614257813</v>
       </c>
       <c r="F81">
-        <v>26214254535284.977</v>
+        <v>26455316837566.195</v>
       </c>
       <c r="G81">
         <v>267549728031.87335</v>
@@ -4587,13 +4589,13 @@
         <v>267549.72803187335</v>
       </c>
       <c r="I81">
-        <v>267549728.03187338</v>
+        <v>2675.4972803187338</v>
       </c>
       <c r="J81">
         <v>0.1185706285131583</v>
       </c>
       <c r="K81">
-        <v>267549728031.87335</v>
+        <v>26754972803.187336</v>
       </c>
       <c r="L81">
         <v>4.1499719979605401E-2</v>
@@ -4609,10 +4611,10 @@
       </c>
       <c r="P81" s="1">
         <f t="shared" si="1"/>
-        <v>26754972803187.336</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.4">
+        <v>26754972803187.332</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4629,7 +4631,7 @@
         <v>196.68441772460938</v>
       </c>
       <c r="F82">
-        <v>19220980535459.234</v>
+        <v>19397733752444.426</v>
       </c>
       <c r="G82">
         <v>196174493836.78021</v>
@@ -4638,13 +4640,13 @@
         <v>196174.4938367802</v>
       </c>
       <c r="I82">
-        <v>196174493.83678022</v>
+        <v>1961.744938367802</v>
       </c>
       <c r="J82">
         <v>8.6939101764688345E-2</v>
       </c>
       <c r="K82">
-        <v>196174493836.78021</v>
+        <v>19617449383.67802</v>
       </c>
       <c r="L82">
         <v>3.0428685617640918E-2</v>
@@ -4663,7 +4665,7 @@
         <v>19617449383678.02</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4680,7 +4682,7 @@
         <v>194.73463439941406</v>
       </c>
       <c r="F83">
-        <v>14006616049966.941</v>
+        <v>14135418763300.99</v>
       </c>
       <c r="G83">
         <v>142955288305.88541</v>
@@ -4689,13 +4691,13 @@
         <v>142955.28830588539</v>
       </c>
       <c r="I83">
-        <v>142955288.3058854</v>
+        <v>1429.5528830588539</v>
       </c>
       <c r="J83">
         <v>6.3353824010201495E-2</v>
       </c>
       <c r="K83">
-        <v>142955288305.88541</v>
+        <v>14295528830.588539</v>
       </c>
       <c r="L83">
         <v>2.2173838403570525E-2</v>
@@ -4711,10 +4713,10 @@
       </c>
       <c r="P83" s="1">
         <f t="shared" si="1"/>
-        <v>14295528830588.537</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.4">
+        <v>14295528830588.535</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4731,7 +4733,7 @@
         <v>192.78546142578125</v>
       </c>
       <c r="F84">
-        <v>10142173151812.254</v>
+        <v>10235439035334.51</v>
       </c>
       <c r="G84">
         <v>103513745346.71802</v>
@@ -4740,13 +4742,13 @@
         <v>103513.74534671802</v>
       </c>
       <c r="I84">
-        <v>103513745.34671801</v>
+        <v>1035.1374534671802</v>
       </c>
       <c r="J84">
         <v>4.5874424675360528E-2</v>
       </c>
       <c r="K84">
-        <v>103513745346.71802</v>
+        <v>10351374534.671801</v>
       </c>
       <c r="L84">
         <v>1.6056048636376184E-2</v>
@@ -4762,10 +4764,10 @@
       </c>
       <c r="P84" s="1">
         <f t="shared" si="1"/>
-        <v>10351374534671.801</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.4">
+        <v>10351374534671.799</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4782,7 +4784,7 @@
         <v>190.83688354492188</v>
       </c>
       <c r="F85">
-        <v>7296006046199.3428</v>
+        <v>7363099009403.2793</v>
       </c>
       <c r="G85">
         <v>74464998833.060165</v>
@@ -4791,13 +4793,13 @@
         <v>74464.998833060163</v>
       </c>
       <c r="I85">
-        <v>74464998.833060175</v>
+        <v>744.64998833060167</v>
       </c>
       <c r="J85">
         <v>3.3000824851579354E-2</v>
       </c>
       <c r="K85">
-        <v>74464998833.060165</v>
+        <v>7446499883.3060169</v>
       </c>
       <c r="L85">
         <v>1.1550288698052772E-2</v>
@@ -4813,10 +4815,10 @@
       </c>
       <c r="P85" s="1">
         <f t="shared" si="1"/>
-        <v>7446499883306.0176</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.4">
+        <v>7446499883306.0166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4833,7 +4835,7 @@
         <v>191</v>
       </c>
       <c r="F86">
-        <v>6179367387286.0996</v>
+        <v>6236191911020.5283</v>
       </c>
       <c r="G86">
         <v>63068284533.976006</v>
@@ -4842,13 +4844,13 @@
         <v>63068.28453397601</v>
       </c>
       <c r="I86">
-        <v>63068284.533976011</v>
+        <v>630.68284533976009</v>
       </c>
       <c r="J86">
         <v>2.795011675567606E-2</v>
       </c>
       <c r="K86">
-        <v>63068284533.976006</v>
+        <v>6306828453.3976011</v>
       </c>
       <c r="L86">
         <v>9.7825408644866205E-3</v>
@@ -4864,10 +4866,10 @@
       </c>
       <c r="P86" s="1">
         <f t="shared" si="1"/>
-        <v>6306828453397.6006</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.4">
+        <v>6306828453397.5996</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4884,7 +4886,7 @@
         <v>190</v>
       </c>
       <c r="F87">
-        <v>4764785921459.8652</v>
+        <v>4808602168935.3828</v>
       </c>
       <c r="G87">
         <v>48630685862.18058</v>
@@ -4893,13 +4895,13 @@
         <v>48630.68586218058</v>
       </c>
       <c r="I87">
-        <v>48630685.862180583</v>
+        <v>486.30685862180576</v>
       </c>
       <c r="J87">
         <v>2.1551772936273684E-2</v>
       </c>
       <c r="K87">
-        <v>48630685862.18058</v>
+        <v>4863068586.2180576</v>
       </c>
       <c r="L87">
         <v>7.5431205276957885E-3</v>
@@ -4915,10 +4917,10 @@
       </c>
       <c r="P87" s="1">
         <f t="shared" si="1"/>
-        <v>4863068586218.0576</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.4">
+        <v>4863068586218.0566</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4935,7 +4937,7 @@
         <v>188</v>
       </c>
       <c r="F88">
-        <v>3369772748807.4189</v>
+        <v>3400760667075.269</v>
       </c>
       <c r="G88">
         <v>34392806450.364403</v>
@@ -4944,13 +4946,13 @@
         <v>34392.806450364398</v>
       </c>
       <c r="I88">
-        <v>34392806.450364403</v>
+        <v>343.92806450364401</v>
       </c>
       <c r="J88">
         <v>1.5241939160802661E-2</v>
       </c>
       <c r="K88">
-        <v>34392806450.364403</v>
+        <v>3439280645.0364399</v>
       </c>
       <c r="L88">
         <v>5.3346787062809311E-3</v>
@@ -4966,10 +4968,10 @@
       </c>
       <c r="P88" s="1">
         <f t="shared" si="1"/>
-        <v>3439280645036.4395</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.4">
+        <v>3439280645036.4399</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4986,7 +4988,7 @@
         <v>187</v>
       </c>
       <c r="F89">
-        <v>2579173136897.9795</v>
+        <v>2602890821241.2676</v>
       </c>
       <c r="G89">
         <v>26323734302.470276</v>
@@ -4995,13 +4997,13 @@
         <v>26323.734302470275</v>
       </c>
       <c r="I89">
-        <v>26323734.302470274</v>
+        <v>263.23734302470274</v>
       </c>
       <c r="J89">
         <v>1.1665949892819372E-2</v>
       </c>
       <c r="K89">
-        <v>26323734302.470276</v>
+        <v>2632373430.2470274</v>
       </c>
       <c r="L89">
         <v>4.0830824624867798E-3</v>
@@ -5020,7 +5022,7 @@
         <v>2632373430247.0273</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5037,7 +5039,7 @@
         <v>187</v>
       </c>
       <c r="F90">
-        <v>2148308081797.8162</v>
+        <v>2168063596550.6946</v>
       </c>
       <c r="G90">
         <v>21926209736.0051</v>
@@ -5046,13 +5048,13 @@
         <v>21926.209736005101</v>
       </c>
       <c r="I90">
-        <v>21926209.736005101</v>
+        <v>219.262097360051</v>
       </c>
       <c r="J90">
         <v>9.7170888134849431E-3</v>
       </c>
       <c r="K90">
-        <v>21926209736.0051</v>
+        <v>2192620973.6005101</v>
       </c>
       <c r="L90">
         <v>3.4009810847197299E-3</v>
@@ -5071,7 +5073,7 @@
         <v>2192620973600.5103</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5088,7 +5090,7 @@
         <v>187</v>
       </c>
       <c r="F91">
-        <v>1789421403430.333</v>
+        <v>1805876650810.4019</v>
       </c>
       <c r="G91">
         <v>18263315829.85807</v>
@@ -5097,13 +5099,13 @@
         <v>18263.315829858067</v>
       </c>
       <c r="I91">
-        <v>18263315.829858072</v>
+        <v>182.6331582985807</v>
       </c>
       <c r="J91">
         <v>8.0937956940199465E-3</v>
       </c>
       <c r="K91">
-        <v>18263315829.85807</v>
+        <v>1826331582.9858069</v>
       </c>
       <c r="L91">
         <v>2.8328284929069812E-3</v>
@@ -5119,10 +5121,10 @@
       </c>
       <c r="P91" s="1">
         <f t="shared" si="1"/>
-        <v>1826331582985.8071</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1826331582985.8069</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5139,7 +5141,7 @@
         <v>188</v>
       </c>
       <c r="F92">
-        <v>1628373010252.396</v>
+        <v>1643347281075.0002</v>
       </c>
       <c r="G92">
         <v>16619612640.178223</v>
@@ -5148,13 +5150,13 @@
         <v>16619.612640178224</v>
       </c>
       <c r="I92">
-        <v>16619612.640178224</v>
+        <v>166.19612640178224</v>
       </c>
       <c r="J92">
         <v>7.3653519698454097E-3</v>
       </c>
       <c r="K92">
-        <v>16619612640.178223</v>
+        <v>1661961264.0178223</v>
       </c>
       <c r="L92">
         <v>2.5778731894458935E-3</v>
@@ -5170,10 +5172,10 @@
       </c>
       <c r="P92" s="1">
         <f t="shared" si="1"/>
-        <v>1661961264017.822</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1661961264017.8218</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5190,7 +5192,7 @@
         <v>189</v>
       </c>
       <c r="F93">
-        <v>1483298607518.821</v>
+        <v>1496938796173.3457</v>
       </c>
       <c r="G93">
         <v>15138944290.692677</v>
@@ -5199,13 +5201,13 @@
         <v>15138.944290692676</v>
       </c>
       <c r="I93">
-        <v>15138944.290692678</v>
+        <v>151.38944290692677</v>
       </c>
       <c r="J93">
         <v>6.7091607708877083E-3</v>
       </c>
       <c r="K93">
-        <v>15138944290.692677</v>
+        <v>1513894429.0692675</v>
       </c>
       <c r="L93">
         <v>2.3482062698106979E-3</v>
@@ -5224,7 +5226,7 @@
         <v>1513894429069.2676</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5241,7 +5243,7 @@
         <v>189</v>
       </c>
       <c r="F94">
-        <v>1237897529175.437</v>
+        <v>1249281046794.4331</v>
       </c>
       <c r="G94">
         <v>12634314922.685087</v>
@@ -5250,13 +5252,13 @@
         <v>12634.314922685087</v>
       </c>
       <c r="I94">
-        <v>12634314.922685089</v>
+        <v>126.34314922685088</v>
       </c>
       <c r="J94">
         <v>5.5991784115642278E-3</v>
       </c>
       <c r="K94">
-        <v>12634314922.685087</v>
+        <v>1263431492.2685089</v>
       </c>
       <c r="L94">
         <v>1.9597124440474799E-3</v>
@@ -5272,10 +5274,10 @@
       </c>
       <c r="P94" s="1">
         <f t="shared" si="1"/>
-        <v>1263431492268.5085</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1263431492268.5088</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5292,7 +5294,7 @@
         <v>190</v>
       </c>
       <c r="F95">
-        <v>1129794251615.8704</v>
+        <v>1140183667917.2959</v>
       </c>
       <c r="G95">
         <v>11530983814.356785</v>
@@ -5301,13 +5303,13 @@
         <v>11530.983814356785</v>
       </c>
       <c r="I95">
-        <v>11530983.814356785</v>
+        <v>115.30983814356784</v>
       </c>
       <c r="J95">
         <v>5.1102126258953245E-3</v>
       </c>
       <c r="K95">
-        <v>11530983814.356785</v>
+        <v>1153098381.4356785</v>
       </c>
       <c r="L95">
         <v>1.7885744190633635E-3</v>
@@ -5326,7 +5328,7 @@
         <v>1153098381435.6785</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5343,7 +5345,7 @@
         <v>191</v>
       </c>
       <c r="F96">
-        <v>1032118538143.9788</v>
+        <v>1041609743423.0463</v>
       </c>
       <c r="G96">
         <v>10534079227.978104</v>
@@ -5352,13 +5354,13 @@
         <v>10534.079227978104</v>
       </c>
       <c r="I96">
-        <v>10534079.227978105</v>
+        <v>105.34079227978103</v>
       </c>
       <c r="J96">
         <v>4.6684121268102024E-3</v>
       </c>
       <c r="K96">
-        <v>10534079227.978104</v>
+        <v>1053407922.7978103</v>
       </c>
       <c r="L96">
         <v>1.6339442443835707E-3</v>
@@ -5377,7 +5379,7 @@
         <v>1053407922797.8103</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5394,7 +5396,7 @@
         <v>192</v>
       </c>
       <c r="F97">
-        <v>943775842578.11304</v>
+        <v>952454661849.62988</v>
       </c>
       <c r="G97">
         <v>9632429931.0112457</v>
@@ -5403,13 +5405,13 @@
         <v>9632.4299310112456</v>
       </c>
       <c r="I97">
-        <v>9632429.9310112465</v>
+        <v>96.324299310112451</v>
       </c>
       <c r="J97">
         <v>4.2688261334838645E-3</v>
       </c>
       <c r="K97">
-        <v>9632429931.0112457</v>
+        <v>963242993.10112453</v>
       </c>
       <c r="L97">
         <v>1.4940891467193525E-3</v>
@@ -5428,7 +5430,7 @@
         <v>963242993101.12451</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5445,7 +5447,7 @@
         <v>193</v>
       </c>
       <c r="F98">
-        <v>863795299825.69983</v>
+        <v>871738630176.57434</v>
       </c>
       <c r="G98">
         <v>8816127013.3583126</v>
@@ -5454,13 +5456,13 @@
         <v>8816.1270133583112</v>
       </c>
       <c r="I98">
-        <v>8816127.0133583117</v>
+        <v>88.161270133583116</v>
       </c>
       <c r="J98">
         <v>3.9070632914311801E-3</v>
       </c>
       <c r="K98">
-        <v>8816127013.3583126</v>
+        <v>881612701.33583117</v>
       </c>
       <c r="L98">
         <v>1.3674721520009129E-3</v>
@@ -5479,7 +5481,7 @@
         <v>881612701335.83093</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5496,7 +5498,7 @@
         <v>193</v>
       </c>
       <c r="F99">
-        <v>723593732262.42224</v>
+        <v>730247790297.17017</v>
       </c>
       <c r="G99">
         <v>7385192129.4116125</v>
@@ -5505,13 +5507,13 @@
         <v>7385.1921294116128</v>
       </c>
       <c r="I99">
-        <v>7385192.1294116136</v>
+        <v>73.851921294116124</v>
       </c>
       <c r="J99">
         <v>3.2729125868161831E-3</v>
       </c>
       <c r="K99">
-        <v>7385192129.4116125</v>
+        <v>738519212.94116127</v>
       </c>
       <c r="L99">
         <v>1.1455194053856638E-3</v>
@@ -5530,7 +5532,7 @@
         <v>738519212941.16125</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5547,7 +5549,7 @@
         <v>194</v>
       </c>
       <c r="F100">
-        <v>663482886071.88477</v>
+        <v>669584173897.00269</v>
       </c>
       <c r="G100">
         <v>6771684675.7322989</v>
@@ -5556,13 +5558,13 @@
         <v>6771.6846757322983</v>
       </c>
       <c r="I100">
-        <v>6771684.6757322988</v>
+        <v>67.716846757322983</v>
       </c>
       <c r="J100">
         <v>3.0010230770963391E-3</v>
       </c>
       <c r="K100">
-        <v>6771684675.7322989</v>
+        <v>677168467.57322991</v>
       </c>
       <c r="L100">
         <v>1.0503580769837186E-3</v>
@@ -5578,10 +5580,10 @@
       </c>
       <c r="P100" s="1">
         <f t="shared" si="1"/>
-        <v>677168467573.2301</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.4">
+        <v>677168467573.22998</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5598,7 +5600,7 @@
         <v>195</v>
       </c>
       <c r="F101">
-        <v>608906993778.56396</v>
+        <v>614506409989.22986</v>
       </c>
       <c r="G101">
         <v>6214668449.2925768</v>
@@ -5607,13 +5609,13 @@
         <v>6214.668449292577</v>
       </c>
       <c r="I101">
-        <v>6214668.4492925778</v>
+        <v>62.146684492925772</v>
       </c>
       <c r="J101">
         <v>2.7541689145194389E-3</v>
       </c>
       <c r="K101">
-        <v>6214668449.2925768</v>
+        <v>621466844.92925775</v>
       </c>
       <c r="L101">
         <v>9.6395912008180357E-4</v>
@@ -5629,12 +5631,12 @@
       </c>
       <c r="P101" s="1">
         <f t="shared" si="1"/>
-        <v>621466844929.25793</v>
+        <v>621466844929.25781</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>